--- a/Team-Data/2014-15/12-28-2014-15.xlsx
+++ b/Team-Data/2014-15/12-28-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -775,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -927,7 +994,7 @@
         <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
         <v>22</v>
@@ -960,10 +1027,10 @@
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>8</v>
@@ -975,13 +1042,13 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1121,19 +1188,19 @@
         <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM4" t="n">
         <v>17</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
         <v>22</v>
@@ -1142,13 +1209,13 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>19</v>
@@ -1172,13 +1239,13 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
@@ -1300,10 +1367,10 @@
         <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1315,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
@@ -1345,7 +1412,7 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY5" t="n">
         <v>15</v>
@@ -1354,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
         <v>17</v>
@@ -1488,7 +1555,7 @@
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1530,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1571,148 +1638,148 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.621</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.465</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.347</v>
+        <v>0.355</v>
       </c>
       <c r="O7" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0.769</v>
       </c>
       <c r="R7" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S7" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T7" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
         <v>22.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.2</v>
+        <v>103</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM7" t="n">
         <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP7" t="n">
         <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1721,7 +1788,7 @@
         <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.71</v>
+        <v>0.677</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,40 +1838,40 @@
         <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.478</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O8" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="P8" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>12.5</v>
@@ -1813,37 +1880,37 @@
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.8</v>
+        <v>109.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
         <v>6</v>
       </c>
-      <c r="AE8" t="n">
-        <v>4</v>
-      </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1864,22 +1931,22 @@
         <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1891,7 +1958,7 @@
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
         <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.419</v>
+        <v>0.433</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1959,43 +2026,43 @@
         <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.317</v>
+        <v>0.319</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
         <v>32.9</v>
       </c>
       <c r="T9" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="U9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V9" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W9" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
         <v>5.8</v>
@@ -2007,25 +2074,25 @@
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>16</v>
@@ -2037,7 +2104,7 @@
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2046,10 +2113,10 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
@@ -2070,10 +2137,10 @@
         <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2088,7 +2155,7 @@
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.233</v>
+        <v>0.207</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.419</v>
+        <v>0.418</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="M10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="P10" t="n">
         <v>23.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="O10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="R10" t="n">
         <v>12.7</v>
@@ -2171,10 +2238,10 @@
         <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="X10" t="n">
         <v>4.6</v>
@@ -2186,16 +2253,16 @@
         <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.2</v>
+        <v>-6.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2207,31 +2274,31 @@
         <v>27</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,22 +2307,22 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
         <v>18</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
@@ -2264,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -2395,7 +2462,7 @@
         <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2422,7 +2489,7 @@
         <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2434,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -2484,91 +2551,91 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>35.4</v>
+        <v>35.1</v>
       </c>
       <c r="J12" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.712</v>
+        <v>0.716</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
         <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
         <v>29</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
         <v>4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>7</v>
       </c>
       <c r="AH12" t="n">
         <v>5</v>
@@ -2595,7 +2662,7 @@
         <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2607,22 +2674,22 @@
         <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2765,13 +2832,13 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2786,13 +2853,13 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2804,16 +2871,16 @@
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2956,13 +3023,13 @@
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2971,7 +3038,7 @@
         <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3042,82 +3109,82 @@
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.434</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.751</v>
       </c>
       <c r="R15" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S15" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.7</v>
+        <v>102.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
@@ -3126,46 +3193,46 @@
         <v>1</v>
       </c>
       <c r="AK15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL15" t="n">
         <v>23</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>16</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
@@ -3174,13 +3241,13 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>4.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
@@ -3320,7 +3387,7 @@
         <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
@@ -3335,13 +3402,13 @@
         <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>10</v>
@@ -3350,13 +3417,13 @@
         <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3496,13 +3563,13 @@
         <v>12</v>
       </c>
       <c r="AM17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
         <v>13</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3660,7 +3727,7 @@
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
@@ -3672,10 +3739,10 @@
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
@@ -3684,7 +3751,7 @@
         <v>11</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
         <v>22</v>
@@ -3696,19 +3763,19 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
         <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
         <v>24</v>
@@ -3717,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3726,7 +3793,7 @@
         <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3854,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3863,10 +3930,10 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3875,13 +3942,13 @@
         <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU19" t="n">
         <v>12</v>
@@ -3890,16 +3957,16 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -3937,106 +4004,106 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.337</v>
+        <v>0.334</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.756</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T20" t="n">
-        <v>42.2</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK20" t="n">
         <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4048,49 +4115,49 @@
         <v>21</v>
       </c>
       <c r="AO20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="n">
         <v>18</v>
       </c>
-      <c r="AP20" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" t="n">
         <v>28</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>29</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J21" t="n">
-        <v>81.7</v>
+        <v>81.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.453</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.353</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.793</v>
+        <v>0.796</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="T21" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="U21" t="n">
         <v>21.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.8</v>
+        <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4212,22 +4279,22 @@
         <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
         <v>20</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>22</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4257,23 +4324,23 @@
         <v>19</v>
       </c>
       <c r="AX21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC21" t="n">
         <v>27</v>
       </c>
-      <c r="AY21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>28</v>
-      </c>
       <c r="BD21" t="n">
         <v>10</v>
       </c>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -4301,100 +4368,100 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.469</v>
+        <v>0.484</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="J22" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="N22" t="n">
         <v>0.324</v>
       </c>
       <c r="O22" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P22" t="n">
         <v>23.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.735</v>
+        <v>0.739</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S22" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="T22" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
       <c r="U22" t="n">
         <v>19.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W22" t="n">
         <v>6.7</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
         <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>98</v>
+        <v>97.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>14</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI22" t="n">
         <v>23</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>19</v>
       </c>
       <c r="AJ22" t="n">
         <v>16</v>
@@ -4403,16 +4470,16 @@
         <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
@@ -4424,7 +4491,7 @@
         <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>2</v>
@@ -4433,28 +4500,28 @@
         <v>30</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
         <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -4483,91 +4550,91 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="N23" t="n">
         <v>0.377</v>
       </c>
       <c r="O23" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
         <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
@@ -4576,16 +4643,16 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4606,13 +4673,13 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AU23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,13 +4691,13 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4761,13 +4828,13 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
@@ -4812,7 +4879,7 @@
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -4847,88 +4914,88 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
         <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J25" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L25" t="n">
         <v>10.1</v>
       </c>
       <c r="M25" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O25" t="n">
         <v>17.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.7</v>
+        <v>105.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -4937,16 +5004,16 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4973,13 +5040,13 @@
         <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>17</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -4991,16 +5058,16 @@
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>0.781</v>
+        <v>0.774</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
@@ -5047,67 +5114,67 @@
         <v>39.3</v>
       </c>
       <c r="J26" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0.454</v>
       </c>
       <c r="L26" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="M26" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.375</v>
       </c>
       <c r="O26" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="P26" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S26" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="T26" t="n">
         <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,10 +5186,10 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
         <v>4</v>
@@ -5131,13 +5198,13 @@
         <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
@@ -5146,13 +5213,13 @@
         <v>28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT26" t="n">
         <v>1</v>
@@ -5161,22 +5228,22 @@
         <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
         <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-1.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
       </c>
       <c r="AF27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
@@ -5304,7 +5371,7 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5331,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
         <v>7</v>
@@ -5340,7 +5407,7 @@
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5355,13 +5422,13 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -5411,34 +5478,34 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="T28" t="n">
         <v>44.4</v>
@@ -5450,28 +5517,28 @@
         <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.9</v>
+        <v>102.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5492,25 +5559,25 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>9</v>
       </c>
       <c r="AM28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP28" t="n">
         <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5525,10 +5592,10 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW28" t="n">
         <v>17</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>15</v>
       </c>
       <c r="AX28" t="n">
         <v>6</v>
@@ -5537,13 +5604,13 @@
         <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -5575,88 +5642,88 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.774</v>
+        <v>0.767</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="J29" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O29" t="n">
         <v>20.6</v>
       </c>
       <c r="P29" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.79</v>
       </c>
       <c r="R29" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X29" t="n">
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA29" t="n">
         <v>22.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>108.5</v>
+        <v>108.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF29" t="n">
         <v>2</v>
@@ -5665,16 +5732,16 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5689,19 +5756,19 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>16</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
@@ -5719,7 +5786,7 @@
         <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5850,13 +5917,13 @@
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5868,19 +5935,19 @@
         <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>21</v>
@@ -5889,7 +5956,7 @@
         <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>7</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>6</v>
       </c>
       <c r="AH31" t="n">
         <v>10</v>
@@ -6050,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>23</v>
@@ -6071,22 +6138,22 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-28-2014-15</t>
+          <t>2014-12-28</t>
         </is>
       </c>
     </row>
